--- a/assets/prizes.xlsx
+++ b/assets/prizes.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="47">
   <si>
     <t>event_group</t>
   </si>
@@ -47,10 +47,10 @@
     <t>A</t>
   </si>
   <si>
-    <t>✨ＰＣ的蒂安希</t>
-  </si>
-  <si>
-    <t>✨異色的蒼響</t>
+    <t>厄鬼椪</t>
+  </si>
+  <si>
+    <t>✨異色的古簡蝸</t>
   </si>
   <si>
     <t>自選閃蛋 3 顆</t>
@@ -59,13 +59,13 @@
     <t>B</t>
   </si>
   <si>
-    <t>✨姬美雅的異色沙奈朵(貴重球)</t>
+    <t>鐵斑葉</t>
   </si>
   <si>
     <t>✨吼叫尾</t>
   </si>
   <si>
-    <t>✨振翼髮</t>
+    <t>✨猛惡菇</t>
   </si>
   <si>
     <t>自選閃蛋 2 顆</t>
@@ -74,22 +74,29 @@
     <t>C</t>
   </si>
   <si>
-    <t>✨木棉球</t>
-  </si>
-  <si>
-    <t>✨小仙奶</t>
-  </si>
-  <si>
-    <t>✨狗仔包</t>
-  </si>
-  <si>
-    <t>✨花蓓蓓</t>
-  </si>
-  <si>
-    <t>✨皮寶寶</t>
+    <t>✨新葉喵</t>
+  </si>
+  <si>
+    <t>✨木木梟</t>
+  </si>
+  <si>
+    <t>✨木守宮</t>
+  </si>
+  <si>
+    <t>✨菊草葉</t>
+  </si>
+  <si>
+    <t>✨妙蛙種子</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>自選閃蛋</t>
     </r>
     <r>
@@ -117,22 +124,25 @@
     <t>Group2</t>
   </si>
   <si>
-    <t>ＸＹ＆Ｚ的大嘴娃(貴重球)</t>
-  </si>
-  <si>
-    <t>✨布莉姆溫(超極巨)</t>
-  </si>
-  <si>
-    <t>✨綿綿泡芙</t>
-  </si>
-  <si>
-    <t>✨粉香香</t>
-  </si>
-  <si>
-    <t>✨小鍛匠</t>
-  </si>
-  <si>
-    <t>✨波克比</t>
+    <t>蕾冠王</t>
+  </si>
+  <si>
+    <t>薩戮德</t>
+  </si>
+  <si>
+    <t>寶可夢紙片的妙蛙花</t>
+  </si>
+  <si>
+    <t>強力組隊的風妖精</t>
+  </si>
+  <si>
+    <t>世錦賽的椰蛋樹</t>
+  </si>
+  <si>
+    <t>✨啃果蟲</t>
+  </si>
+  <si>
+    <t>✨敲音猴</t>
   </si>
   <si>
     <t>自選閃蛋 1 顆</t>
@@ -141,22 +151,22 @@
     <t>Group3</t>
   </si>
   <si>
+    <t>✨謝米</t>
+  </si>
+  <si>
     <t>自選色違 3 隻</t>
   </si>
   <si>
-    <t>中秋賞月的皮皮</t>
+    <t>ＰＣ的葉伊布</t>
   </si>
   <si>
     <t>自選色違 2 隻</t>
   </si>
   <si>
-    <t>✨魔尼尼</t>
-  </si>
-  <si>
-    <t>✨露力麗</t>
-  </si>
-  <si>
-    <t>✨寶寶丁</t>
+    <t>✨含羞苞</t>
+  </si>
+  <si>
+    <t>✨草苗龜</t>
   </si>
   <si>
     <t>自選色違 1 隻</t>
@@ -165,25 +175,28 @@
     <t>Group4</t>
   </si>
   <si>
-    <t>生日的差不多娃娃(貴重球)</t>
+    <t>✨畢力吉翁</t>
+  </si>
+  <si>
+    <t>自選色違 3 隻(頭目)</t>
+  </si>
+  <si>
+    <t>✨妙蛙花(頭目)</t>
+  </si>
+  <si>
+    <t>✨葉伊布(頭目)</t>
   </si>
   <si>
     <t>自選色違 2 隻(頭目)</t>
   </si>
   <si>
-    <t>✨沙奈朵(頭目)</t>
+    <t>✨喇叭芽</t>
+  </si>
+  <si>
+    <t>✨哈力栗</t>
   </si>
   <si>
     <t>自選色違 1 隻(頭目)</t>
-  </si>
-  <si>
-    <t>自選色違 2 隻(一般)</t>
-  </si>
-  <si>
-    <t>✨差不多娃娃</t>
-  </si>
-  <si>
-    <t>自選色違 1 隻(一般)</t>
   </si>
 </sst>
 </file>
@@ -196,7 +209,7 @@
     <numFmt numFmtId="176" formatCode="_-&quot;NT$&quot;* #,##0.00_-;\-&quot;NT$&quot;* #,##0.00_-;_-&quot;NT$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;NT$&quot;* #,##0_-;\-&quot;NT$&quot;* #,##0_-;_-&quot;NT$&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="22">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -220,20 +233,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -377,15 +376,8 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="37">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -466,12 +458,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -581,12 +567,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -714,19 +694,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -735,131 +724,122 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -872,40 +852,25 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1267,7 +1232,7 @@
       <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="3">
@@ -1281,7 +1246,7 @@
       <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="3">
@@ -1295,7 +1260,7 @@
       <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="3">
@@ -1309,7 +1274,7 @@
       <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="3">
@@ -1323,7 +1288,7 @@
       <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="3">
@@ -1337,7 +1302,7 @@
       <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="3">
@@ -1351,7 +1316,7 @@
       <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="3">
@@ -1365,7 +1330,7 @@
       <c r="B9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="3">
@@ -1379,7 +1344,7 @@
       <c r="B10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="3">
@@ -1393,7 +1358,7 @@
       <c r="B11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D11" s="3">
@@ -1407,7 +1372,7 @@
       <c r="B12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D12" s="3">
@@ -1421,7 +1386,7 @@
       <c r="B13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="3">
@@ -1435,7 +1400,7 @@
       <c r="B14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D14" s="3">
@@ -1443,492 +1408,492 @@
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="7">
+      <c r="C15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="5">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="7">
+      <c r="C16" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="5">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="5">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="7">
+      <c r="C18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="5">
         <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="7">
+      <c r="C19" s="6" t="s">
         <v>25</v>
       </c>
+      <c r="D19" s="5">
+        <v>25</v>
+      </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="7">
+      <c r="C20" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="5">
         <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="5">
         <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="9" t="s">
+      <c r="B22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="7">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="7" t="s">
+      <c r="D24" s="5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="9" t="s">
+      <c r="B25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="7">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="9" t="s">
+      <c r="D30" s="7">
         <v>25</v>
       </c>
-      <c r="D24" s="7">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="7">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D26" s="7">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27" s="7">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="10" t="s">
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" s="7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33" s="7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="10">
+      <c r="C39" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" s="9">
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="10" t="s">
+    <row r="40" spans="1:4">
+      <c r="A40" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" s="10">
+      <c r="C40" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D40" s="9">
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30" s="10" t="s">
+    <row r="41" spans="1:4">
+      <c r="A41" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30" s="10">
+      <c r="C41" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D41" s="9">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="10" t="s">
+    <row r="42" spans="1:4">
+      <c r="A42" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C31" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D31" s="10">
+      <c r="C42" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D42" s="9">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B32" s="10" t="s">
+    <row r="43" spans="1:4">
+      <c r="A43" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C32" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D32" s="10">
+      <c r="C43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D43" s="9">
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D33" s="10">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D34" s="10">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="11" t="s">
+    <row r="44" spans="1:4">
+      <c r="A44" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="10">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="10">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D37" s="10">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D38" s="10">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" s="14" t="s">
+      <c r="D45" s="9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D39" s="13">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D40" s="13">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="D41" s="13">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D42" s="13">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C43" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="D43" s="13">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="D44" s="13">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C45" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" s="13">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C46" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D46" s="13">
+      <c r="B46" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="9">
         <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C47" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D47" s="13">
+      <c r="A47" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D47" s="9">
         <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B48" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C48" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D48" s="13">
+      <c r="A48" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D48" s="9">
         <v>60</v>
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D49" s="13">
+      <c r="A49" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D49" s="9">
         <v>60</v>
       </c>
     </row>
